--- a/MagicWildCardRom_Explaination.xlsx
+++ b/MagicWildCardRom_Explaination.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>MENU ROM HACKING:</t>
   </si>
@@ -44,43 +44,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">- Menu Num files:     Offset:  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0x1ED6</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Number of file in SDcard(ex: 19 files =&gt; 0x13)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">- Len of files name LOW:   Offset: </t>
     </r>
     <r>
@@ -271,21 +234,86 @@
       <t>FD 0E</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">- Menu Num files:     </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Offset Low:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0x1ED6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : Number of file in SDcard(ex: 300 files =&gt; 0x012C =&gt;  0x1ED6 is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0x2C)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Offset High:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0x1ED7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : Number of file in SDcard(ex: 300 files =&gt; 0x012C =&gt;  0x1ED7 is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0x01)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -645,9 +673,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>57151</xdr:colOff>
+      <xdr:colOff>238125</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -657,7 +685,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2819401" y="1800225"/>
-          <a:ext cx="285750" cy="180975"/>
+          <a:ext cx="466724" cy="161925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -897,7 +925,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1600" b="1" baseline="0"/>
-            <a:t>(0x13h)</a:t>
+            <a:t>(0x0013h)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1600" b="1"/>
         </a:p>
@@ -2453,29 +2481,37 @@
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2485,12 +2521,12 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2500,12 +2536,12 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C75" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C109" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="3:4" x14ac:dyDescent="0.25">
@@ -2530,7 +2566,7 @@
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2550,12 +2586,12 @@
   <sheetData>
     <row r="6" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/MagicWildCardRom_Explaination.xlsx
+++ b/MagicWildCardRom_Explaination.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Menu_Rom" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>MENU ROM HACKING:</t>
   </si>
@@ -306,6 +306,9 @@
       </rPr>
       <t>0x01)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -2104,7 +2107,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100"/>
-            <a:t>- Last 2 Bytes: Dont know (checksum??????)</a:t>
+            <a:t>- Last 2 Bytes: Dont know (checksum???????)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2475,7 +2478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
@@ -2569,6 +2572,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="175" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G175" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
